--- a/registration_forms/017_game_schedule_submission_form--registration_forms.xlsx
+++ b/registration_forms/017_game_schedule_submission_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_input_1</t>
+          <t>team_info_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user_input_2</t>
+          <t>team_info_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,214 +554,214 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_input_3</t>
+          <t>multiple_schedules_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Schedule Dates</t>
+          <t>Multiple Schedules</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user_input_4</t>
+          <t>schedule_start_date_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Schedule Time</t>
+          <t>Schedule Start Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_input_5</t>
+          <t>schedule_end_date_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Game Type</t>
+          <t>Schedule End Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user_input_6</t>
+          <t>schedule_time_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Schedule Start Time</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>user_input_7</t>
+          <t>schedule_end_time_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Venue</t>
+          <t>Schedule End Time</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_input_8</t>
+          <t>game_type_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Team Size</t>
+          <t>Game Type</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>user_input_9</t>
+          <t>game_type_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Game Type</t>
+          <t>Multiple Game Types</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>user_input_10</t>
+          <t>venue_info_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Venue</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>user_input_11</t>
+          <t>multiple_venues_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Venue</t>
+          <t>Multiple Venues</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,156 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>user_input_12</t>
+          <t>team_size_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Team Size</t>
+          <t>Team Size 12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>capacity_13</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Estimated Capacity</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>open_to_public_14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Open to Public</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fee_15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Game Fee</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fee_waiver_16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fee Waiver</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>confirm_submission_17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Confirm Your Schedule Submission</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>confirmation_18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Is This Correct?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -799,11 +937,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -827,136 +965,272 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>user_input_5_choices</t>
+          <t>multiple_schedules_3_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>user_input_5_choices</t>
+          <t>multiple_schedules_3_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>user_input_6_choices</t>
+          <t>game_type_8_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>user_input_6_choices</t>
+          <t>game_type_8_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>user_input_9_choices</t>
+          <t>game_type_9_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>user_input_9_choices</t>
+          <t>game_type_9_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>user_input_10_choices</t>
+          <t>multiple_venues_11_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>user_input_10_choices</t>
+          <t>multiple_venues_11_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>open_to_public_14_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>open_to_public_14_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>fee_15_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fee_15_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>fee_waiver_16_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fee_waiver_16_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>confirmation_18_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>confirmation_18_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
